--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.0%</t>
+          <t>-657.1%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.8%</t>
         </is>
       </c>
     </row>
@@ -48931,10 +48931,10 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.954692192325834</v>
+        <v>-4.955211809903434</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.204898735425412</v>
+        <v>2.204690888394373</v>
       </c>
       <c r="F2060" t="n">
         <v>0.6882420566346017</v>

--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-30.2%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-657.1%</t>
+          <t>-662.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-157.8%</t>
         </is>
       </c>
     </row>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161977</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,7 +47706,7 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321634</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
@@ -47729,7 +47729,7 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
@@ -47821,7 +47821,7 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378394</v>
+        <v>3.749882691378393</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
@@ -47844,7 +47844,7 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006977</v>
+        <v>3.715819895006976</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
@@ -47867,7 +47867,7 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787387</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
@@ -47890,7 +47890,7 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585939</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
@@ -47913,7 +47913,7 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
@@ -47936,7 +47936,7 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237094</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
@@ -47959,7 +47959,7 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423387</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609753</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
@@ -48005,7 +48005,7 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973158</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
@@ -48028,7 +48028,7 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251947</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
@@ -48051,7 +48051,7 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916203</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
@@ -48074,7 +48074,7 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.66796230683033</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
@@ -48097,7 +48097,7 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071552</v>
+        <v>3.696539468071551</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
@@ -48120,7 +48120,7 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868147</v>
+        <v>3.750044015868146</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
@@ -48143,7 +48143,7 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332691</v>
+        <v>3.78363286733269</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231809</v>
+        <v>3.798296784231807</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
@@ -48189,7 +48189,7 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818524</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
@@ -48212,7 +48212,7 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77723741205179</v>
+        <v>3.777237412051787</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
@@ -48235,7 +48235,7 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
@@ -48258,7 +48258,7 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474158</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
@@ -48281,7 +48281,7 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
@@ -48304,7 +48304,7 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700477</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
@@ -48327,7 +48327,7 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
@@ -48350,7 +48350,7 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833458</v>
+        <v>3.775028860833456</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
@@ -48373,7 +48373,7 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
@@ -48396,7 +48396,7 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
@@ -48419,7 +48419,7 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735282</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
@@ -48442,7 +48442,7 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496552</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
@@ -48465,7 +48465,7 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108857</v>
+        <v>3.815643212108855</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
@@ -48488,7 +48488,7 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121467</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
@@ -48511,7 +48511,7 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906081</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
@@ -48534,7 +48534,7 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912986</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539895</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.72501084481101</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.61232244438292</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760317</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781708</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082837</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943589</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677827</v>
+        <v>3.730590658677824</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073886</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903171</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568386</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682208</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539111</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983741</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969752</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073542</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
@@ -48925,16 +48925,16 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.756501996614277</v>
+        <v>3.756501996614273</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.955211809903434</v>
+        <v>-5.006863552973638</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.204690888394373</v>
+        <v>2.184030191166291</v>
       </c>
       <c r="F2060" t="n">
         <v>0.6882420566346017</v>

--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.3%</t>
+          <t>-660.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.8%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.1%</t>
+          <t>-328.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-153.1%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -47683,7 +47683,7 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161977</v>
       </c>
       <c r="C2006" t="n">
         <v>3.467544857421219</v>
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321634</v>
       </c>
       <c r="C2007" t="n">
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.833171184452031</v>
+        <v>-2.859089463984018</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33681105387196</v>
+        <v>2.326443742059165</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.269739551583441</v>
+        <v>1.243821272051453</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.232279682916585</v>
+        <v>4.216728715197392</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347704</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.909501162052937</v>
+        <v>-2.935419441584924</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304390875725373</v>
+        <v>2.294023563912578</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.269739551583441</v>
+        <v>1.243821272051453</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.23039149581036</v>
+        <v>4.214840528091167</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.137673161909277</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.207942305385699</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.0415675517271</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>4.088308525499418</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.299241587436533</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>2.14174894538495</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.9147846279292203</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>4.010672781430842</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.405624600002098</v>
+        <v>-3.431542879534086</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.112269147224642</v>
+        <v>2.101901835411847</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.9147846279292203</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>4.02374618829676</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378393</v>
+        <v>3.749882691378394</v>
       </c>
       <c r="C2012" t="n">
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591492910841328</v>
+        <v>-3.617411190373316</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02992701967189</v>
+        <v>2.019559707859095</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.7562190346092726</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.920612029087732</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006976</v>
+        <v>3.715819895006977</v>
       </c>
       <c r="C2013" t="n">
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619393697950801</v>
+        <v>-3.645311977482789</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.017290745955103</v>
+        <v>2.006923434142307</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.7216221104663378</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.898377915728974</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787387</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741919800653695</v>
+        <v>-3.767838080185683</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.965044748851144</v>
+        <v>1.954677437038349</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.599096007763444</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.821626698084436</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585939</v>
       </c>
       <c r="C2015" t="n">
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972434296839284</v>
+        <v>-3.998352576371271</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.939544909967412</v>
+        <v>1.929177598154617</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.3685815115778552</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.750023959963587</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.229155114834107</v>
+        <v>-4.255073394366095</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97716830177133</v>
+        <v>1.966800989958535</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.825286934479144</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237094</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.383141532610248</v>
+        <v>-4.409059812142235</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.984554003806513</v>
+        <v>1.974186691993718</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.894267203624784</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423387</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.332619628782582</v>
+        <v>-4.358537908314569</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.990813967457701</v>
+        <v>1.980446655644906</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.880318405744905</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609753</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.585094782790306</v>
+        <v>-4.611013062322294</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901694394910025</v>
+        <v>1.89132708309723</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.892188894800319</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973158</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.877990539269718</v>
+        <v>-4.903908818801706</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785746626837204</v>
+        <v>1.775379315024409</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.893399429319263</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251946</v>
+        <v>3.663509457251947</v>
       </c>
       <c r="C2021" t="n">
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.064654667404526</v>
+        <v>-5.090572946936514</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715202717810602</v>
+        <v>1.704835405997807</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.2334279666094805</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.881477789051848</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916202</v>
+        <v>3.652149152916203</v>
       </c>
       <c r="C2022" t="n">
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210675354318488</v>
+        <v>-5.236593633850476</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651872295781207</v>
+        <v>1.641504983968411</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2243448748156235</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.871105786711723</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830329</v>
+        <v>3.66796230683033</v>
       </c>
       <c r="C2023" t="n">
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.302389363428073</v>
+        <v>-5.328307642960061</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777390748836417</v>
+        <v>1.767023437023622</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2243448748156235</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>4.033309843410768</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071551</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.334041022488043</v>
+        <v>-5.35995930202003</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759576723176243</v>
+        <v>1.749209411363448</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2450946971031708</v>
+        <v>0.2191764175711833</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.04060637474711</v>
+        <v>4.025055407027918</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868146</v>
+        <v>3.750044015868147</v>
       </c>
       <c r="C2025" t="n">
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.415975840756926</v>
+        <v>-5.441894120288914</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.737032213437181</v>
+        <v>1.726664901624386</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2351599515160906</v>
+        <v>0.2092416719841032</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.044874944963353</v>
+        <v>4.029323977244161</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78363286733269</v>
+        <v>3.783632867332691</v>
       </c>
       <c r="C2026" t="n">
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.517951963005333</v>
+        <v>-5.543870242537321</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.70516740299372</v>
+        <v>1.694800091180925</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.133183829267683</v>
+        <v>0.1072655497356956</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.992614910070211</v>
+        <v>3.977063942351019</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231807</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.407945679528112</v>
+        <v>-5.433863959060099</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741322803628784</v>
+        <v>1.73095549181599</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1563884011849582</v>
+        <v>0.1304701216529708</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.998690540464752</v>
+        <v>3.983139572745559</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818524</v>
       </c>
       <c r="C2028" t="n">
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.264886103787186</v>
+        <v>-5.290804383319173</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802796644647129</v>
+        <v>1.792429332834334</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1644018277749375</v>
+        <v>0.1384835482429501</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007748607140713</v>
+        <v>3.992197639421521</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051787</v>
+        <v>3.77723741205179</v>
       </c>
       <c r="C2029" t="n">
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.963439378315348</v>
+        <v>-4.989357657847336</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.9306362177184</v>
+        <v>1.920268905905605</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4399302737147873</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.195877525306352</v>
+        <v>4.18032655758716</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.988029622550532</v>
+        <v>-5.01394790208252</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.921771297777037</v>
+        <v>1.911403985964242</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4399302737147873</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196848703059063</v>
+        <v>4.18129773533987</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474158</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.936991246544012</v>
+        <v>-4.962909526075999</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.9430295525594</v>
+        <v>1.932662240746605</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4399302737147873</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.197691607438817</v>
+        <v>4.182140639719625</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969542</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.895851951677381</v>
+        <v>-4.921770231209369</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978523369380198</v>
+        <v>1.968156057567403</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5069878481134056</v>
+        <v>0.4810695685814181</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.241413283232942</v>
+        <v>4.225862315513749</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700477</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.799217039658741</v>
+        <v>-4.825135319190728</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833361330311589</v>
+        <v>1.822994018498794</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6036227601320455</v>
+        <v>0.5777044806000581</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.11557822656806</v>
+        <v>4.100027258848868</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.929797774189583</v>
+        <v>-4.955716053721571</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784631080573216</v>
+        <v>1.77426376876042</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.473042025601203</v>
+        <v>0.4471237460692156</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.040731829923518</v>
+        <v>4.025180862204325</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833456</v>
+        <v>3.775028860833458</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.811764869176562</v>
+        <v>-4.791219719530609</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.816271061654507</v>
+        <v>1.824489121512888</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.591074930614224</v>
+        <v>0.6116200802601774</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.095978392007413</v>
+        <v>4.108305481794986</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.839134801860994</v>
+        <v>-4.818589652215041</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.804510799017163</v>
+        <v>1.812728858875545</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.591074930614224</v>
+        <v>0.6116200802601774</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.095166102443843</v>
+        <v>4.107493192231415</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.849519996750884</v>
+        <v>-4.828974847104931</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.81022550018628</v>
+        <v>1.818443560044661</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5806897357243347</v>
+        <v>0.6012348853702881</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.098803764634982</v>
+        <v>4.111130854422554</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735282</v>
       </c>
       <c r="C2038" t="n">
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.868108155473108</v>
+        <v>-4.847563005827156</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.873627242473815</v>
+        <v>1.881845302332196</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5621015770021094</v>
+        <v>0.5826467266480628</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.158487875178071</v>
+        <v>4.170814964965644</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496552</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.868406702169144</v>
+        <v>-4.847861552523192</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.870376834613699</v>
+        <v>1.878594894472081</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5621015770021094</v>
+        <v>0.5826467266480628</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.155356885996371</v>
+        <v>4.167683975783943</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108855</v>
+        <v>3.815643212108857</v>
       </c>
       <c r="C2040" t="n">
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.767583568478717</v>
+        <v>-4.747038418832764</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.915236983029262</v>
+        <v>1.923455042887643</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5745657924864632</v>
+        <v>0.5951109421324167</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.167366310226374</v>
+        <v>4.179693400013946</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.57680220772631</v>
+        <v>-4.556257058080357</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.991678780808768</v>
+        <v>1.999896840667149</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7653471532388706</v>
+        <v>0.785892302884824</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.281964380156362</v>
+        <v>4.294291469943934</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.558285353684489</v>
+        <v>-4.537740204038537</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.978922368163093</v>
+        <v>1.987140428021474</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7782772826640788</v>
+        <v>0.7988224323100322</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.269559303549083</v>
+        <v>4.281886393336655</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912986</v>
       </c>
       <c r="C2043" t="n">
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.533092169183171</v>
+        <v>-4.512547019537219</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.023966578575678</v>
+        <v>2.032184638434059</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8034704671653972</v>
+        <v>0.8240156168113506</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.319642150861933</v>
+        <v>4.331969240649505</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.743767956539895</v>
       </c>
       <c r="C2044" t="n">
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.521038042270209</v>
+        <v>-4.500492892624256</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.022474797242301</v>
+        <v>2.030692857100682</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.81552459407836</v>
+        <v>0.8360697437243134</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.320561194911148</v>
+        <v>4.33288828469872</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.527661288960567</v>
+        <v>-4.507116139314614</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.021706128750294</v>
+        <v>2.029924188608675</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8089013473880016</v>
+        <v>0.829446497033955</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.318467877081069</v>
+        <v>4.330794966868641</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.424780699431974</v>
+        <v>-4.404235549786021</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.075709390439613</v>
+        <v>2.083927450297995</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.393047256676107</v>
+        <v>4.405374346463679</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760317</v>
       </c>
       <c r="C2047" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.448222738612061</v>
+        <v>-4.427677588966108</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.086535244941173</v>
+        <v>2.094753304799554</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.413249926849701</v>
+        <v>4.425577016637273</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781708</v>
       </c>
       <c r="C2048" t="n">
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.466295246903672</v>
+        <v>-4.44575009725772</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.079306241624528</v>
+        <v>2.087524301482909</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.413249926849701</v>
+        <v>4.425577016637273</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.670068888082837</v>
       </c>
       <c r="C2049" t="n">
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.697469040780304</v>
+        <v>-4.676923891134352</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.947088637667342</v>
+        <v>1.955306697525723</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.373501840443168</v>
+        <v>4.38582893023074</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943589</v>
       </c>
       <c r="C2050" t="n">
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.666183020239849</v>
+        <v>-4.645637870593896</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.966625664880464</v>
+        <v>1.974843724738845</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9430679574570499</v>
+        <v>0.9636131071030033</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.399296071764381</v>
+        <v>4.411623161551953</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677824</v>
+        <v>3.730590658677827</v>
       </c>
       <c r="C2051" t="n">
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.513157628126565</v>
+        <v>-4.492612478480612</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.127006821298682</v>
+        <v>2.135224881157063</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.096093349570334</v>
+        <v>1.116638499216287</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.590282306605255</v>
+        <v>4.602609396392828</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.741298518073886</v>
       </c>
       <c r="C2052" t="n">
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.541464941999835</v>
+        <v>-4.520919792353882</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.303150120657667</v>
+        <v>2.311368180516047</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.096093349570334</v>
+        <v>1.116638499216287</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.777748531513549</v>
+        <v>4.790075621301121</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903171</v>
       </c>
       <c r="C2053" t="n">
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.708058167113357</v>
+        <v>-4.687513017467404</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.20591578196634</v>
+        <v>2.214133841824721</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9295001244568115</v>
+        <v>0.950045274102765</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.647195547799517</v>
+        <v>4.659522637587089</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568386</v>
       </c>
       <c r="C2054" t="n">
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.534993787731057</v>
+        <v>-4.514448638085105</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.278817936380977</v>
+        <v>2.287035996239358</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9295001244568115</v>
+        <v>0.950045274102765</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.650871950461235</v>
+        <v>4.663199040248807</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.740601586682208</v>
       </c>
       <c r="C2055" t="n">
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.505747807275361</v>
+        <v>-4.485202657629408</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.288134383686751</v>
+        <v>2.296352443545132</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9295001244568115</v>
+        <v>0.950045274102765</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.64849000558473</v>
+        <v>4.660817095372302</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539111</v>
       </c>
       <c r="C2056" t="n">
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.612673355153212</v>
+        <v>-4.592128205507259</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.242657403693246</v>
+        <v>2.250875463551627</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8225745765789602</v>
+        <v>0.8431197262249136</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.581627916015654</v>
+        <v>4.593955005803227</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983741</v>
       </c>
       <c r="C2057" t="n">
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.757691913660461</v>
+        <v>-4.737146764014508</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.18607878243358</v>
+        <v>2.194296842291962</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6775560180717116</v>
+        <v>0.6981011677176651</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.496045583054539</v>
+        <v>4.508372672842111</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969752</v>
       </c>
       <c r="C2058" t="n">
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.876033679445178</v>
+        <v>-4.855488529799225</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.238673315377446</v>
+        <v>2.246891375235828</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6882420566346017</v>
+        <v>0.7087872062805551</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.602388445450027</v>
+        <v>4.614715535237599</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073542</v>
       </c>
       <c r="C2059" t="n">
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.927444101765886</v>
+        <v>-4.906898952119933</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.215894843575102</v>
+        <v>2.224112903433483</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6882420566346017</v>
+        <v>0.7087872062805551</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.600174142575965</v>
+        <v>4.612501232363537</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.756501996614273</v>
+        <v>3.73951271447338</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.006863552973638</v>
+        <v>-4.986318403327685</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.184030191166291</v>
+        <v>2.192248251024672</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6882420566346017</v>
+        <v>0.7087872062805551</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.600077270650255</v>
+        <v>4.612404360437827</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>107.1%</t>
+          <t>111.8%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.5%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.2%</t>
+          <t>-662.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-157.8%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,17 +1260,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.6%</t>
+          <t>-330.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-153.1%</t>
+          <t>-155.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>94.0%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-08-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.0%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>-23.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2060"/>
+  <dimension ref="A1:G2061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.859089463984018</v>
+        <v>-2.833171184452031</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.326443742059165</v>
+        <v>2.33681105387196</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.243821272051453</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.216728715197392</v>
+        <v>4.232279682916585</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.935419441584924</v>
+        <v>-2.909501162052937</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.294023563912578</v>
+        <v>2.304390875725373</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.243821272051453</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.214840528091167</v>
+        <v>4.23039149581036</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.137673161909277</v>
+        <v>-3.11175488237729</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.207942305385699</v>
+        <v>2.218309617198494</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.0415675517271</v>
+        <v>1.067485831259087</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.088308525499418</v>
+        <v>4.10385949321861</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.299241587436533</v>
+        <v>-3.273323307904545</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.14174894538495</v>
+        <v>2.152116257197744</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9147846279292203</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.010672781430842</v>
+        <v>4.026223749150034</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.431542879534086</v>
+        <v>-3.405624600002098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.101901835411847</v>
+        <v>2.112269147224642</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9147846279292203</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.02374618829676</v>
+        <v>4.039297156015953</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.617411190373316</v>
+        <v>-3.591492910841328</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.019559707859095</v>
+        <v>2.02992701967189</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7562190346092726</v>
+        <v>0.7821373141412601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.920612029087732</v>
+        <v>3.936162996806924</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.645311977482789</v>
+        <v>-3.619393697950801</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.006923434142307</v>
+        <v>2.017290745955103</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7216221104663378</v>
+        <v>0.7475403899983253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.898377915728974</v>
+        <v>3.913928883448166</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.767838080185683</v>
+        <v>-3.741919800653695</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.954677437038349</v>
+        <v>1.965044748851144</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.599096007763444</v>
+        <v>0.6250142872954314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.821626698084436</v>
+        <v>3.837177665803628</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.998352576371271</v>
+        <v>-3.972434296839284</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.929177598154617</v>
+        <v>1.939544909967412</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3685815115778552</v>
+        <v>0.3944997911098427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.750023959963587</v>
+        <v>3.765574927682779</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.255073394366095</v>
+        <v>-4.229155114834107</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.966800989958535</v>
+        <v>1.97716830177133</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.825286934479144</v>
+        <v>3.840837902198337</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.409059812142235</v>
+        <v>-4.383141532610248</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.974186691993718</v>
+        <v>1.984554003806513</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.894267203624784</v>
+        <v>3.909818171343977</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.358537908314569</v>
+        <v>-4.332619628782582</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.980446655644906</v>
+        <v>1.990813967457701</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.880318405744905</v>
+        <v>3.895869373464098</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.611013062322294</v>
+        <v>-4.585094782790306</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.89132708309723</v>
+        <v>1.901694394910025</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.892188894800319</v>
+        <v>3.907739862519512</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.903908818801706</v>
+        <v>-4.877990539269718</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.775379315024409</v>
+        <v>1.785746626837204</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.893399429319263</v>
+        <v>3.908950397038455</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.090572946936514</v>
+        <v>-5.064654667404526</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.704835405997807</v>
+        <v>1.715202717810602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2334279666094805</v>
+        <v>0.259346246141468</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.881477789051848</v>
+        <v>3.897028756771041</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.236593633850476</v>
+        <v>-5.210675354318488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.641504983968411</v>
+        <v>1.651872295781207</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2243448748156235</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.871105786711723</v>
+        <v>3.886656754430916</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.328307642960061</v>
+        <v>-5.302389363428073</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.767023437023622</v>
+        <v>1.777390748836417</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2243448748156235</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.033309843410768</v>
+        <v>4.04886081112996</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.35995930202003</v>
+        <v>-5.334041022488043</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.749209411363448</v>
+        <v>1.759576723176243</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2191764175711833</v>
+        <v>0.2450946971031708</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.025055407027918</v>
+        <v>4.04060637474711</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.441894120288914</v>
+        <v>-5.415975840756926</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.726664901624386</v>
+        <v>1.737032213437181</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2092416719841032</v>
+        <v>0.2351599515160906</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.029323977244161</v>
+        <v>4.044874944963353</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.543870242537321</v>
+        <v>-5.517951963005333</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.694800091180925</v>
+        <v>1.70516740299372</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1072655497356956</v>
+        <v>0.133183829267683</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.977063942351019</v>
+        <v>3.992614910070211</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.433863959060099</v>
+        <v>-5.407945679528112</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.73095549181599</v>
+        <v>1.741322803628784</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1304701216529708</v>
+        <v>0.1563884011849582</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.983139572745559</v>
+        <v>3.998690540464752</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.290804383319173</v>
+        <v>-5.264886103787186</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.792429332834334</v>
+        <v>1.802796644647129</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1384835482429501</v>
+        <v>0.1644018277749375</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.992197639421521</v>
+        <v>4.007748607140713</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.989357657847336</v>
+        <v>-4.963439378315348</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.920268905905605</v>
+        <v>1.9306362177184</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4399302737147873</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.18032655758716</v>
+        <v>4.195877525306352</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.01394790208252</v>
+        <v>-4.988029622550532</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.911403985964242</v>
+        <v>1.921771297777037</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4399302737147873</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.18129773533987</v>
+        <v>4.196848703059063</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.962909526075999</v>
+        <v>-4.936991246544012</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.932662240746605</v>
+        <v>1.9430295525594</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4399302737147873</v>
+        <v>0.4658485532467748</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.182140639719625</v>
+        <v>4.197691607438817</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.921770231209369</v>
+        <v>-4.895851951677381</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.968156057567403</v>
+        <v>1.978523369380198</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4810695685814181</v>
+        <v>0.5069878481134056</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.225862315513749</v>
+        <v>4.241413283232942</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.825135319190728</v>
+        <v>-4.799217039658741</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.822994018498794</v>
+        <v>1.833361330311589</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5777044806000581</v>
+        <v>0.6036227601320455</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.100027258848868</v>
+        <v>4.11557822656806</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.955716053721571</v>
+        <v>-4.929797774189583</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.77426376876042</v>
+        <v>1.784631080573216</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4471237460692156</v>
+        <v>0.473042025601203</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.025180862204325</v>
+        <v>4.040731829923518</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.791219719530609</v>
+        <v>-4.811764869176562</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.824489121512888</v>
+        <v>1.816271061654507</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6116200802601774</v>
+        <v>0.591074930614224</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.108305481794986</v>
+        <v>4.095978392007413</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.818589652215041</v>
+        <v>-4.839134801860994</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.812728858875545</v>
+        <v>1.804510799017163</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6116200802601774</v>
+        <v>0.591074930614224</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.107493192231415</v>
+        <v>4.095166102443843</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.828974847104931</v>
+        <v>-4.849519996750884</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.818443560044661</v>
+        <v>1.81022550018628</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6012348853702881</v>
+        <v>0.5806897357243347</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.111130854422554</v>
+        <v>4.098803764634982</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.847563005827156</v>
+        <v>-4.868108155473108</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.881845302332196</v>
+        <v>1.873627242473815</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5826467266480628</v>
+        <v>0.5621015770021094</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.170814964965644</v>
+        <v>4.158487875178071</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.847861552523192</v>
+        <v>-4.868406702169144</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.878594894472081</v>
+        <v>1.870376834613699</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5826467266480628</v>
+        <v>0.5621015770021094</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.167683975783943</v>
+        <v>4.155356885996371</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.747038418832764</v>
+        <v>-4.767583568478717</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.923455042887643</v>
+        <v>1.915236983029262</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5951109421324167</v>
+        <v>0.5745657924864632</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.179693400013946</v>
+        <v>4.167366310226374</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.556257058080357</v>
+        <v>-4.57680220772631</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.999896840667149</v>
+        <v>1.991678780808768</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.785892302884824</v>
+        <v>0.7653471532388706</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.294291469943934</v>
+        <v>4.281964380156362</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.537740204038537</v>
+        <v>-4.558285353684489</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.987140428021474</v>
+        <v>1.978922368163093</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7988224323100322</v>
+        <v>0.7782772826640788</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.281886393336655</v>
+        <v>4.269559303549083</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.512547019537219</v>
+        <v>-4.533092169183171</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.032184638434059</v>
+        <v>2.023966578575678</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8240156168113506</v>
+        <v>0.8034704671653972</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.331969240649505</v>
+        <v>4.319642150861933</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.500492892624256</v>
+        <v>-4.521038042270209</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.030692857100682</v>
+        <v>2.022474797242301</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8360697437243134</v>
+        <v>0.81552459407836</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.33288828469872</v>
+        <v>4.320561194911148</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.507116139314614</v>
+        <v>-4.527661288960567</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.029924188608675</v>
+        <v>2.021706128750294</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.829446497033955</v>
+        <v>0.8089013473880016</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.330794966868641</v>
+        <v>4.318467877081069</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.404235549786021</v>
+        <v>-4.424780699431974</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.083927450297995</v>
+        <v>2.075709390439613</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9323270865625479</v>
+        <v>0.9117819369165945</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.405374346463679</v>
+        <v>4.393047256676107</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.427677588966108</v>
+        <v>-4.448222738612061</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.094753304799554</v>
+        <v>2.086535244941173</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9323270865625479</v>
+        <v>0.9117819369165945</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.425577016637273</v>
+        <v>4.413249926849701</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.44575009725772</v>
+        <v>-4.466295246903672</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.087524301482909</v>
+        <v>2.079306241624528</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9323270865625479</v>
+        <v>0.9117819369165945</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.425577016637273</v>
+        <v>4.413249926849701</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.676923891134352</v>
+        <v>-4.697469040780304</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.955306697525723</v>
+        <v>1.947088637667342</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9323270865625479</v>
+        <v>0.9117819369165945</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.38582893023074</v>
+        <v>4.373501840443168</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.645637870593896</v>
+        <v>-4.666183020239849</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.974843724738845</v>
+        <v>1.966625664880464</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9636131071030033</v>
+        <v>0.9430679574570499</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.411623161551953</v>
+        <v>4.399296071764381</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.492612478480612</v>
+        <v>-4.513157628126565</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.135224881157063</v>
+        <v>2.127006821298682</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.116638499216287</v>
+        <v>1.096093349570334</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.602609396392828</v>
+        <v>4.590282306605255</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.520919792353882</v>
+        <v>-4.541464941999835</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.311368180516047</v>
+        <v>2.303150120657667</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.116638499216287</v>
+        <v>1.096093349570334</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.790075621301121</v>
+        <v>4.777748531513549</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.687513017467404</v>
+        <v>-4.708058167113357</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.214133841824721</v>
+        <v>2.20591578196634</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.950045274102765</v>
+        <v>0.9295001244568115</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.659522637587089</v>
+        <v>4.647195547799517</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.514448638085105</v>
+        <v>-4.534993787731057</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.287035996239358</v>
+        <v>2.278817936380977</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.950045274102765</v>
+        <v>0.9295001244568115</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.663199040248807</v>
+        <v>4.650871950461235</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.485202657629408</v>
+        <v>-4.505747807275361</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.296352443545132</v>
+        <v>2.288134383686751</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.950045274102765</v>
+        <v>0.9295001244568115</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.660817095372302</v>
+        <v>4.64849000558473</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.592128205507259</v>
+        <v>-4.612673355153212</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.250875463551627</v>
+        <v>2.242657403693246</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8431197262249136</v>
+        <v>0.8225745765789602</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.593955005803227</v>
+        <v>4.581627916015654</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.737146764014508</v>
+        <v>-4.757691913660461</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.194296842291962</v>
+        <v>2.18607878243358</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6981011677176651</v>
+        <v>0.6775560180717116</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.508372672842111</v>
+        <v>4.496045583054539</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.855488529799225</v>
+        <v>-4.876033679445178</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.246891375235828</v>
+        <v>2.238673315377446</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7087872062805551</v>
+        <v>0.6882420566346017</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.614715535237599</v>
+        <v>4.602388445450027</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.906898952119933</v>
+        <v>-4.927444101765886</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.224112903433483</v>
+        <v>2.215894843575102</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7087872062805551</v>
+        <v>0.6882420566346017</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.612501232363537</v>
+        <v>4.600174142575965</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,45 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.73951271447338</v>
+        <v>3.704778134720068</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.986318403327685</v>
+        <v>-5.006863552973638</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.192248251024672</v>
+        <v>2.184030191166291</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7087872062805551</v>
+        <v>0.6882420566346017</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.612404360437827</v>
+        <v>4.600077270650255</v>
+      </c>
+    </row>
+    <row r="2061">
+      <c r="A2061" s="2" t="n">
+        <v>45523</v>
+      </c>
+      <c r="B2061" t="n">
+        <v>3.757030851711191</v>
+      </c>
+      <c r="C2061" t="n">
+        <v>4.234682392073224</v>
+      </c>
+      <c r="D2061" t="n">
+        <v>-5.006863552973638</v>
+      </c>
+      <c r="E2061" t="n">
+        <v>2.184030191166291</v>
+      </c>
+      <c r="F2061" t="n">
+        <v>0.6882420566346017</v>
+      </c>
+      <c r="G2061" t="n">
+        <v>4.227746189059592</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>45.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>79.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.7%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-662.3%</t>
+          <t>-666.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.8%</t>
+          <t>-159.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-330.1%</t>
+          <t>-328.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.2%</t>
+          <t>-159.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.1%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-23.3%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.833171184452031</v>
+        <v>-2.878303444521319</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33681105387196</v>
+        <v>2.318758149844245</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.269739551583441</v>
+        <v>1.224607291514153</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.232279682916585</v>
+        <v>4.205200326875012</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.909501162052937</v>
+        <v>-2.954633422122225</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.304390875725373</v>
+        <v>2.286337971697658</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.269739551583441</v>
+        <v>1.224607291514153</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.23039149581036</v>
+        <v>4.203312139768787</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.11175488237729</v>
+        <v>-3.156887142446578</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.218309617198494</v>
+        <v>2.200256713170779</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.067485831259087</v>
+        <v>1.022353571189799</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.10385949321861</v>
+        <v>4.076780137177037</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.273323307904545</v>
+        <v>-3.318455567973833</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.152116257197744</v>
+        <v>2.134063353170029</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.8955706473919199</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.026223749150034</v>
+        <v>3.999144393108462</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.405624600002098</v>
+        <v>-3.450756860071386</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.112269147224642</v>
+        <v>2.094216243196927</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9407029074612078</v>
+        <v>0.8955706473919199</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.039297156015953</v>
+        <v>4.012217799974381</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.591492910841328</v>
+        <v>-3.636625170910616</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.02992701967189</v>
+        <v>2.011874115644175</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7821373141412601</v>
+        <v>0.7370050540719723</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.936162996806924</v>
+        <v>3.909083640765352</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.619393697950801</v>
+        <v>-3.664525958020089</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.017290745955103</v>
+        <v>1.999237841927387</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7475403899983253</v>
+        <v>0.7024081299290375</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.913928883448166</v>
+        <v>3.886849527406593</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.741919800653695</v>
+        <v>-3.787052060722983</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.965044748851144</v>
+        <v>1.946991844823429</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6250142872954314</v>
+        <v>0.5798820272261436</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.837177665803628</v>
+        <v>3.810098309762056</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.972434296839284</v>
+        <v>-4.017566556908572</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.939544909967412</v>
+        <v>1.921492005939696</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3944997911098427</v>
+        <v>0.3493675310405548</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.765574927682779</v>
+        <v>3.738495571641206</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.229155114834107</v>
+        <v>-4.274287374903396</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.97716830177133</v>
+        <v>1.959115397743614</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.24095295689674</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.840837902198337</v>
+        <v>3.813758546156764</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.383141532610248</v>
+        <v>-4.428273792679537</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.984554003806513</v>
+        <v>1.966501099778798</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.24095295689674</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.909818171343977</v>
+        <v>3.882738815302404</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.332619628782582</v>
+        <v>-4.377751888851871</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.990813967457701</v>
+        <v>1.972761063429985</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.24095295689674</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.895869373464098</v>
+        <v>3.868790017422525</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.585094782790306</v>
+        <v>-4.630227042859596</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.901694394910025</v>
+        <v>1.883641490882309</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.24095295689674</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.907739862519512</v>
+        <v>3.880660506477939</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.877990539269718</v>
+        <v>-4.923122799339008</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.785746626837204</v>
+        <v>1.767693722809488</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2860852169660278</v>
+        <v>0.24095295689674</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.908950397038455</v>
+        <v>3.881871040996883</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.064654667404526</v>
+        <v>-5.109786927473816</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.715202717810602</v>
+        <v>1.697149813782886</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.259346246141468</v>
+        <v>0.2142139860721801</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.897028756771041</v>
+        <v>3.869949400729468</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.210675354318488</v>
+        <v>-5.255807614387778</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.651872295781207</v>
+        <v>1.633819391753491</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2051308942783232</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.886656754430916</v>
+        <v>3.859577398389343</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.302389363428073</v>
+        <v>-5.347521623497363</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.777390748836417</v>
+        <v>1.759337844808701</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.250263154347611</v>
+        <v>0.2051308942783232</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.04886081112996</v>
+        <v>4.021781455088387</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.334041022488043</v>
+        <v>-5.379173282557332</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.759576723176243</v>
+        <v>1.741523819148527</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2450946971031708</v>
+        <v>0.1999624370338829</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.04060637474711</v>
+        <v>4.013527018705537</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.415975840756926</v>
+        <v>-5.461108100826215</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.737032213437181</v>
+        <v>1.718979309409465</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2351599515160906</v>
+        <v>0.1900276914468028</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.044874944963353</v>
+        <v>4.01779558892178</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.517951963005333</v>
+        <v>-5.563084223074623</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.70516740299372</v>
+        <v>1.687114498966005</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.133183829267683</v>
+        <v>0.08805156919839519</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.992614910070211</v>
+        <v>3.965535554028638</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.407945679528112</v>
+        <v>-5.453077939597401</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.741322803628784</v>
+        <v>1.723269899601068</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1563884011849582</v>
+        <v>0.1112561411156704</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.998690540464752</v>
+        <v>3.971611184423179</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.264886103787186</v>
+        <v>-5.310018363856475</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.802796644647129</v>
+        <v>1.784743740619414</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1644018277749375</v>
+        <v>0.1192695677056497</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.007748607140713</v>
+        <v>3.98066925109914</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.963439378315348</v>
+        <v>-5.008571638384637</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.9306362177184</v>
+        <v>1.912583313690684</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4207162931774869</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.195877525306352</v>
+        <v>4.168798169264779</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.988029622550532</v>
+        <v>-5.033161882619821</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.921771297777037</v>
+        <v>1.903718393749322</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4207162931774869</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196848703059063</v>
+        <v>4.16976934701749</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.936991246544012</v>
+        <v>-4.982123506613301</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.9430295525594</v>
+        <v>1.924976648531684</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4658485532467748</v>
+        <v>0.4207162931774869</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.197691607438817</v>
+        <v>4.170612251397245</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.895851951677381</v>
+        <v>-4.94098421174667</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.978523369380198</v>
+        <v>1.960470465352483</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5069878481134056</v>
+        <v>0.4618555880441177</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.241413283232942</v>
+        <v>4.214333927191369</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.799217039658741</v>
+        <v>-4.84434929972803</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.833361330311589</v>
+        <v>1.815308426283873</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6036227601320455</v>
+        <v>0.5584905000627577</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.11557822656806</v>
+        <v>4.088498870526487</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.929797774189583</v>
+        <v>-4.974930034258873</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.784631080573216</v>
+        <v>1.7665781765455</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.473042025601203</v>
+        <v>0.4279097655319152</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.040731829923518</v>
+        <v>4.013652473881946</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833458</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.811764869176562</v>
+        <v>-4.856897129245851</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.816271061654507</v>
+        <v>1.798218157626791</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.591074930614224</v>
+        <v>0.5459426705449362</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.095978392007413</v>
+        <v>4.06889903596584</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077629</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.839134801860994</v>
+        <v>-4.884267061930283</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.804510799017163</v>
+        <v>1.786457894989448</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.591074930614224</v>
+        <v>0.5459426705449362</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.095166102443843</v>
+        <v>4.068086746402271</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.849519996750884</v>
+        <v>-4.894652256820173</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.81022550018628</v>
+        <v>1.792172596158564</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5806897357243347</v>
+        <v>0.5355574756550469</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.098803764634982</v>
+        <v>4.071724408593409</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.868108155473108</v>
+        <v>-4.913240415542398</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.873627242473815</v>
+        <v>1.855574338446099</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5621015770021094</v>
+        <v>0.5169693169328216</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.158487875178071</v>
+        <v>4.1314085191365</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.868406702169144</v>
+        <v>-4.913538962238434</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.870376834613699</v>
+        <v>1.852323930585984</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5621015770021094</v>
+        <v>0.5169693169328216</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.155356885996371</v>
+        <v>4.128277529954798</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.767583568478717</v>
+        <v>-4.812715828548006</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.915236983029262</v>
+        <v>1.897184079001546</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5745657924864632</v>
+        <v>0.5294335324171754</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.167366310226374</v>
+        <v>4.140286954184801</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.57680220772631</v>
+        <v>-4.621934467795599</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.991678780808768</v>
+        <v>1.973625876781052</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7653471532388706</v>
+        <v>0.7202148931695828</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.281964380156362</v>
+        <v>4.254885024114789</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.558285353684489</v>
+        <v>-4.603417613753779</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.978922368163093</v>
+        <v>1.960869464135377</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7782772826640788</v>
+        <v>0.733145022594791</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.269559303549083</v>
+        <v>4.24247994750751</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.533092169183171</v>
+        <v>-4.578224429252461</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.023966578575678</v>
+        <v>2.005913674547962</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8034704671653972</v>
+        <v>0.7583382070961093</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.319642150861933</v>
+        <v>4.29256279482036</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.521038042270209</v>
+        <v>-4.566170302339498</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.022474797242301</v>
+        <v>2.004421893214586</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.81552459407836</v>
+        <v>0.7703923340090721</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.320561194911148</v>
+        <v>4.293481838869575</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.527661288960567</v>
+        <v>-4.572793549029856</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.021706128750294</v>
+        <v>2.003653224722578</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8089013473880016</v>
+        <v>0.7637690873187137</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.318467877081069</v>
+        <v>4.291388521039496</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.424780699431974</v>
+        <v>-4.469912959501263</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.075709390439613</v>
+        <v>2.057656486411898</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.8666496768473066</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.393047256676107</v>
+        <v>4.365967900634534</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.448222738612061</v>
+        <v>-4.49335499868135</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.086535244941173</v>
+        <v>2.068482340913457</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.8666496768473066</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.413249926849701</v>
+        <v>4.386170570808129</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.466295246903672</v>
+        <v>-4.511427506972962</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.079306241624528</v>
+        <v>2.061253337596813</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.8666496768473066</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.413249926849701</v>
+        <v>4.386170570808129</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.697469040780304</v>
+        <v>-4.742601300849594</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.947088637667342</v>
+        <v>1.929035733639626</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9117819369165945</v>
+        <v>0.8666496768473066</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.373501840443168</v>
+        <v>4.346422484401595</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.666183020239849</v>
+        <v>-4.711315280309138</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.966625664880464</v>
+        <v>1.948572760852748</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9430679574570499</v>
+        <v>0.897935697387762</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.399296071764381</v>
+        <v>4.372216715722809</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.513157628126565</v>
+        <v>-4.558289888195854</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.127006821298682</v>
+        <v>2.108953917270966</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.096093349570334</v>
+        <v>1.050961089501046</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.590282306605255</v>
+        <v>4.563202950563683</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.541464941999835</v>
+        <v>-4.586597202069124</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.303150120657667</v>
+        <v>2.285097216629951</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.096093349570334</v>
+        <v>1.050961089501046</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.777748531513549</v>
+        <v>4.750669175471976</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.708058167113357</v>
+        <v>-4.753190427182647</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.20591578196634</v>
+        <v>2.187862877938624</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9295001244568115</v>
+        <v>0.8843678643875237</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.647195547799517</v>
+        <v>4.620116191757944</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.534993787731057</v>
+        <v>-4.580126047800347</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.278817936380977</v>
+        <v>2.260765032353262</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9295001244568115</v>
+        <v>0.8843678643875237</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.650871950461235</v>
+        <v>4.623792594419662</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.505747807275361</v>
+        <v>-4.55088006734465</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.288134383686751</v>
+        <v>2.270081479659035</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9295001244568115</v>
+        <v>0.8843678643875237</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.64849000558473</v>
+        <v>4.621410649543157</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.612673355153212</v>
+        <v>-4.657805615222501</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.242657403693246</v>
+        <v>2.22460449966553</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8225745765789602</v>
+        <v>0.7774423165096723</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.581627916015654</v>
+        <v>4.554548559974082</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.757691913660461</v>
+        <v>-4.80282417372975</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.18607878243358</v>
+        <v>2.168025878405865</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6775560180717116</v>
+        <v>0.6324237580024238</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.496045583054539</v>
+        <v>4.468966227012967</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.876033679445178</v>
+        <v>-4.921165939514467</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.238673315377446</v>
+        <v>2.220620411349731</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6882420566346017</v>
+        <v>0.6431097965653139</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.602388445450027</v>
+        <v>4.575309089408454</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.927444101765886</v>
+        <v>-4.972576361835175</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.215894843575102</v>
+        <v>2.197841939547386</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6882420566346017</v>
+        <v>0.6431097965653139</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.600174142575965</v>
+        <v>4.573094786534392</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.006863552973638</v>
+        <v>-5.051995813042927</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.184030191166291</v>
+        <v>2.165977287138575</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6882420566346017</v>
+        <v>0.6431097965653139</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.600077270650255</v>
+        <v>4.572997914608682</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.757030851711191</v>
+        <v>3.739867861186503</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.234682392073224</v>
+        <v>4.234480098878111</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.006863552973638</v>
+        <v>-5.051995813042927</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.184030191166291</v>
+        <v>2.165977287138575</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6882420566346017</v>
+        <v>0.6431097965653139</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.227746189059592</v>
+        <v>4.227543895864478</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-666.8%</t>
+          <t>-660.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-159.6%</t>
+          <t>-157.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.7%</t>
+          <t>-328.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-159.7%</t>
+          <t>-153.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.878303444521319</v>
+        <v>-2.859089463984018</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.318758149844245</v>
+        <v>2.326443742059165</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.224607291514153</v>
+        <v>1.243821272051453</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.205200326875012</v>
+        <v>4.216728715197392</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.954633422122225</v>
+        <v>-2.935419441584924</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.286337971697658</v>
+        <v>2.294023563912578</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.224607291514153</v>
+        <v>1.243821272051453</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.203312139768787</v>
+        <v>4.214840528091167</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.156887142446578</v>
+        <v>-3.137673161909277</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.200256713170779</v>
+        <v>2.207942305385699</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.022353571189799</v>
+        <v>1.0415675517271</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.076780137177037</v>
+        <v>4.088308525499418</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.318455567973833</v>
+        <v>-3.299241587436533</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.134063353170029</v>
+        <v>2.14174894538495</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8955706473919199</v>
+        <v>0.9147846279292203</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.999144393108462</v>
+        <v>4.010672781430842</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.450756860071386</v>
+        <v>-3.431542879534086</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.094216243196927</v>
+        <v>2.101901835411847</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8955706473919199</v>
+        <v>0.9147846279292203</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.012217799974381</v>
+        <v>4.02374618829676</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.636625170910616</v>
+        <v>-3.617411190373316</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.011874115644175</v>
+        <v>2.019559707859095</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7370050540719723</v>
+        <v>0.7562190346092726</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.909083640765352</v>
+        <v>3.920612029087732</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.664525958020089</v>
+        <v>-3.645311977482789</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.999237841927387</v>
+        <v>2.006923434142307</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7024081299290375</v>
+        <v>0.7216221104663378</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.886849527406593</v>
+        <v>3.898377915728974</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.787052060722983</v>
+        <v>-3.767838080185683</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.946991844823429</v>
+        <v>1.954677437038349</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.5798820272261436</v>
+        <v>0.599096007763444</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.810098309762056</v>
+        <v>3.821626698084436</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.017566556908572</v>
+        <v>-3.998352576371271</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.921492005939696</v>
+        <v>1.929177598154617</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3493675310405548</v>
+        <v>0.3685815115778552</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.738495571641206</v>
+        <v>3.750023959963587</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.274287374903396</v>
+        <v>-4.255073394366095</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.959115397743614</v>
+        <v>1.966800989958535</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.24095295689674</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.813758546156764</v>
+        <v>3.825286934479144</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.428273792679537</v>
+        <v>-4.409059812142235</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.966501099778798</v>
+        <v>1.974186691993718</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.24095295689674</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.882738815302404</v>
+        <v>3.894267203624784</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.377751888851871</v>
+        <v>-4.358537908314569</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.972761063429985</v>
+        <v>1.980446655644906</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.24095295689674</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.868790017422525</v>
+        <v>3.880318405744905</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.630227042859596</v>
+        <v>-4.611013062322294</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.883641490882309</v>
+        <v>1.89132708309723</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.24095295689674</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.880660506477939</v>
+        <v>3.892188894800319</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.923122799339008</v>
+        <v>-4.903908818801706</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.767693722809488</v>
+        <v>1.775379315024409</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.24095295689674</v>
+        <v>0.2601669374340404</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.881871040996883</v>
+        <v>3.893399429319263</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.109786927473816</v>
+        <v>-5.090572946936514</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.697149813782886</v>
+        <v>1.704835405997807</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2142139860721801</v>
+        <v>0.2334279666094805</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.869949400729468</v>
+        <v>3.881477789051848</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.255807614387778</v>
+        <v>-5.236593633850476</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.633819391753491</v>
+        <v>1.641504983968411</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2051308942783232</v>
+        <v>0.2243448748156235</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.859577398389343</v>
+        <v>3.871105786711723</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.347521623497363</v>
+        <v>-5.328307642960061</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.759337844808701</v>
+        <v>1.767023437023622</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2051308942783232</v>
+        <v>0.2243448748156235</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.021781455088387</v>
+        <v>4.033309843410768</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.379173282557332</v>
+        <v>-5.35995930202003</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.741523819148527</v>
+        <v>1.749209411363448</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1999624370338829</v>
+        <v>0.2191764175711833</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.013527018705537</v>
+        <v>4.025055407027918</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.461108100826215</v>
+        <v>-5.441894120288914</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.718979309409465</v>
+        <v>1.726664901624386</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1900276914468028</v>
+        <v>0.2092416719841032</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.01779558892178</v>
+        <v>4.029323977244161</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.563084223074623</v>
+        <v>-5.543870242537321</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.687114498966005</v>
+        <v>1.694800091180925</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.08805156919839519</v>
+        <v>0.1072655497356956</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.965535554028638</v>
+        <v>3.977063942351019</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.453077939597401</v>
+        <v>-5.433863959060099</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.723269899601068</v>
+        <v>1.73095549181599</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1112561411156704</v>
+        <v>0.1304701216529708</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.971611184423179</v>
+        <v>3.983139572745559</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.310018363856475</v>
+        <v>-5.290804383319173</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.784743740619414</v>
+        <v>1.792429332834334</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1192695677056497</v>
+        <v>0.1384835482429501</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.98066925109914</v>
+        <v>3.992197639421521</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.008571638384637</v>
+        <v>-4.989357657847336</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.912583313690684</v>
+        <v>1.920268905905605</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4207162931774869</v>
+        <v>0.4399302737147873</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.168798169264779</v>
+        <v>4.18032655758716</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.033161882619821</v>
+        <v>-5.01394790208252</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.903718393749322</v>
+        <v>1.911403985964242</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4207162931774869</v>
+        <v>0.4399302737147873</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.16976934701749</v>
+        <v>4.18129773533987</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.982123506613301</v>
+        <v>-4.962909526075999</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.924976648531684</v>
+        <v>1.932662240746605</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4207162931774869</v>
+        <v>0.4399302737147873</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.170612251397245</v>
+        <v>4.182140639719625</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.94098421174667</v>
+        <v>-4.921770231209369</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.960470465352483</v>
+        <v>1.968156057567403</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4618555880441177</v>
+        <v>0.4810695685814181</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.214333927191369</v>
+        <v>4.225862315513749</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.84434929972803</v>
+        <v>-4.825135319190728</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.815308426283873</v>
+        <v>1.822994018498794</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5584905000627577</v>
+        <v>0.5777044806000581</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.088498870526487</v>
+        <v>4.100027258848868</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.974930034258873</v>
+        <v>-4.955716053721571</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.7665781765455</v>
+        <v>1.77426376876042</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4279097655319152</v>
+        <v>0.4471237460692156</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.013652473881946</v>
+        <v>4.025180862204325</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.856897129245851</v>
+        <v>-4.791219719530609</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.798218157626791</v>
+        <v>1.824489121512888</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5459426705449362</v>
+        <v>0.6116200802601774</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.06889903596584</v>
+        <v>4.108305481794986</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.884267061930283</v>
+        <v>-4.818589652215041</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.786457894989448</v>
+        <v>1.812728858875545</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5459426705449362</v>
+        <v>0.6116200802601774</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.068086746402271</v>
+        <v>4.107493192231415</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.894652256820173</v>
+        <v>-4.828974847104931</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.792172596158564</v>
+        <v>1.818443560044661</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5355574756550469</v>
+        <v>0.6012348853702881</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.071724408593409</v>
+        <v>4.111130854422554</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.913240415542398</v>
+        <v>-4.847563005827156</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.855574338446099</v>
+        <v>1.881845302332196</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5169693169328216</v>
+        <v>0.5826467266480628</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.1314085191365</v>
+        <v>4.170814964965644</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.913538962238434</v>
+        <v>-4.847861552523192</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.852323930585984</v>
+        <v>1.878594894472081</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5169693169328216</v>
+        <v>0.5826467266480628</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.128277529954798</v>
+        <v>4.167683975783943</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.812715828548006</v>
+        <v>-4.747038418832764</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.897184079001546</v>
+        <v>1.923455042887643</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5294335324171754</v>
+        <v>0.5951109421324167</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.140286954184801</v>
+        <v>4.179693400013946</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.621934467795599</v>
+        <v>-4.556257058080357</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.973625876781052</v>
+        <v>1.999896840667149</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7202148931695828</v>
+        <v>0.785892302884824</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.254885024114789</v>
+        <v>4.294291469943934</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.603417613753779</v>
+        <v>-4.537740204038537</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.960869464135377</v>
+        <v>1.987140428021474</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.733145022594791</v>
+        <v>0.7988224323100322</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.24247994750751</v>
+        <v>4.281886393336655</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.578224429252461</v>
+        <v>-4.512547019537219</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.005913674547962</v>
+        <v>2.032184638434059</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.7583382070961093</v>
+        <v>0.8240156168113506</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.29256279482036</v>
+        <v>4.331969240649505</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.566170302339498</v>
+        <v>-4.500492892624256</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.004421893214586</v>
+        <v>2.030692857100682</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.7703923340090721</v>
+        <v>0.8360697437243134</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.293481838869575</v>
+        <v>4.33288828469872</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.572793549029856</v>
+        <v>-4.507116139314614</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003653224722578</v>
+        <v>2.029924188608675</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7637690873187137</v>
+        <v>0.829446497033955</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.291388521039496</v>
+        <v>4.330794966868641</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.469912959501263</v>
+        <v>-4.404235549786021</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.057656486411898</v>
+        <v>2.083927450297995</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8666496768473066</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.365967900634534</v>
+        <v>4.405374346463679</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.49335499868135</v>
+        <v>-4.427677588966108</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.068482340913457</v>
+        <v>2.094753304799554</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8666496768473066</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.386170570808129</v>
+        <v>4.425577016637273</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.511427506972962</v>
+        <v>-4.44575009725772</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.061253337596813</v>
+        <v>2.087524301482909</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8666496768473066</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.386170570808129</v>
+        <v>4.425577016637273</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.742601300849594</v>
+        <v>-4.676923891134352</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.929035733639626</v>
+        <v>1.955306697525723</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8666496768473066</v>
+        <v>0.9323270865625479</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.346422484401595</v>
+        <v>4.38582893023074</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.711315280309138</v>
+        <v>-4.645637870593896</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.948572760852748</v>
+        <v>1.974843724738845</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.897935697387762</v>
+        <v>0.9636131071030033</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.372216715722809</v>
+        <v>4.411623161551953</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.558289888195854</v>
+        <v>-4.492612478480612</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.108953917270966</v>
+        <v>2.135224881157063</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.050961089501046</v>
+        <v>1.116638499216287</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.563202950563683</v>
+        <v>4.602609396392828</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.586597202069124</v>
+        <v>-4.520919792353882</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.285097216629951</v>
+        <v>2.311368180516047</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.050961089501046</v>
+        <v>1.116638499216287</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.750669175471976</v>
+        <v>4.790075621301121</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.753190427182647</v>
+        <v>-4.687513017467404</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.187862877938624</v>
+        <v>2.214133841824721</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.8843678643875237</v>
+        <v>0.950045274102765</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.620116191757944</v>
+        <v>4.659522637587089</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.580126047800347</v>
+        <v>-4.514448638085105</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.260765032353262</v>
+        <v>2.287035996239358</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.8843678643875237</v>
+        <v>0.950045274102765</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.623792594419662</v>
+        <v>4.663199040248807</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.55088006734465</v>
+        <v>-4.485202657629408</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.270081479659035</v>
+        <v>2.296352443545132</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.8843678643875237</v>
+        <v>0.950045274102765</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.621410649543157</v>
+        <v>4.660817095372302</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.657805615222501</v>
+        <v>-4.592128205507259</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.22460449966553</v>
+        <v>2.250875463551627</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.7774423165096723</v>
+        <v>0.8431197262249136</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.554548559974082</v>
+        <v>4.593955005803227</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.80282417372975</v>
+        <v>-4.737146764014508</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.168025878405865</v>
+        <v>2.194296842291962</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6324237580024238</v>
+        <v>0.6981011677176651</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.468966227012967</v>
+        <v>4.508372672842111</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.921165939514467</v>
+        <v>-4.855488529799225</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.220620411349731</v>
+        <v>2.246891375235828</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.6431097965653139</v>
+        <v>0.7087872062805551</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.575309089408454</v>
+        <v>4.614715535237599</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.972576361835175</v>
+        <v>-4.906898952119933</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.197841939547386</v>
+        <v>2.224112903433483</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.6431097965653139</v>
+        <v>0.7087872062805551</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.573094786534392</v>
+        <v>4.612501232363537</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.051995813042927</v>
+        <v>-4.986318403327685</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.165977287138575</v>
+        <v>2.192248251024672</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.6431097965653139</v>
+        <v>0.7087872062805551</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.572997914608682</v>
+        <v>4.612404360437827</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.234480098878111</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.051995813042927</v>
+        <v>-4.986318403327685</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.165977287138575</v>
+        <v>2.192248251024672</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.6431097965653139</v>
+        <v>0.7087872062805551</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.227543895864478</v>
+        <v>4.227543895864479</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.5%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>111.8%</t>
+          <t>107.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>107.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-30.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.0%</t>
+          <t>-47.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-660.2%</t>
+          <t>-655.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.0%</t>
+          <t>-155.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.0%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
     </row>
@@ -48951,19 +48951,19 @@
         <v>3.739867861186503</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.234480098878111</v>
+        <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.986318403327685</v>
+        <v>-4.936158757282457</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.192248251024672</v>
+        <v>2.212306003000807</v>
       </c>
       <c r="F2061" t="n">
         <v>0.7087872062805551</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.227543895864479</v>
+        <v>4.61239825399587</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240819.xlsx
+++ b/tame_output/ON/bt/strategyON_20240819.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>58.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.2%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-30.3%</t>
+          <t>-42.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.9%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-655.2%</t>
+          <t>-661.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.0%</t>
+          <t>-157.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-328.6%</t>
+          <t>-325.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-153.1%</t>
+          <t>-140.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -47712,16 +47712,16 @@
         <v>3.47043595196652</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.859089463984018</v>
+        <v>-2.833171184452031</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.326443742059165</v>
+        <v>2.33681105387196</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.243821272051453</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.216728715197392</v>
+        <v>4.232279682916585</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.468547764860295</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.935419441584924</v>
+        <v>-2.909501162052937</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.294023563912578</v>
+        <v>2.304390875725373</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.243821272051453</v>
+        <v>1.269739551583441</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.214840528091167</v>
+        <v>4.23039149581036</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.463367994463157</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.137673161909277</v>
+        <v>-3.11175488237729</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.207942305385699</v>
+        <v>2.218309617198494</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.0415675517271</v>
+        <v>1.067485831259087</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.088308525499418</v>
+        <v>4.10385949321861</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.46180200467331</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.299241587436533</v>
+        <v>-3.273323307904545</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.14174894538495</v>
+        <v>2.152116257197744</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9147846279292203</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.010672781430842</v>
+        <v>4.026223749150034</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.474875411539228</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.431542879534086</v>
+        <v>-3.405624600002098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.101901835411847</v>
+        <v>2.112269147224642</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9147846279292203</v>
+        <v>0.9407029074612078</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.02374618829676</v>
+        <v>4.039297156015953</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.466880608322168</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.617411190373316</v>
+        <v>-3.591492910841328</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.019559707859095</v>
+        <v>2.02992701967189</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7562190346092726</v>
+        <v>0.7821373141412601</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.920612029087732</v>
+        <v>3.936162996806924</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.46540464944917</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.645311977482789</v>
+        <v>-3.619393697950801</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.006923434142307</v>
+        <v>2.017290745955103</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7216221104663378</v>
+        <v>0.7475403899983253</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.898377915728974</v>
+        <v>3.913928883448166</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.462169093426369</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.767838080185683</v>
+        <v>-3.741919800653695</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.954677437038349</v>
+        <v>1.965044748851144</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.599096007763444</v>
+        <v>0.6250142872954314</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.821626698084436</v>
+        <v>3.837177665803628</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.528875053016873</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.998352576371271</v>
+        <v>-3.972434296839284</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.929177598154617</v>
+        <v>1.939544909967412</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3685815115778552</v>
+        <v>0.3944997911098427</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.750023959963587</v>
+        <v>3.765574927682779</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.66918677201872</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.255073394366095</v>
+        <v>-4.229155114834107</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.966800989958535</v>
+        <v>1.97716830177133</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.825286934479144</v>
+        <v>3.840837902198337</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.73816704116436</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.409059812142235</v>
+        <v>-4.383141532610248</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.974186691993718</v>
+        <v>1.984554003806513</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.894267203624784</v>
+        <v>3.909818171343977</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.724218243284481</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.358537908314569</v>
+        <v>-4.332619628782582</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.980446655644906</v>
+        <v>1.990813967457701</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.880318405744905</v>
+        <v>3.895869373464098</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.736088732339895</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.611013062322294</v>
+        <v>-4.585094782790306</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.89132708309723</v>
+        <v>1.901694394910025</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.892188894800319</v>
+        <v>3.907739862519512</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.737299266858838</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.903908818801706</v>
+        <v>-4.877990539269718</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.775379315024409</v>
+        <v>1.785746626837204</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2601669374340404</v>
+        <v>0.2860852169660278</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.893399429319263</v>
+        <v>3.908950397038455</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.74142100908616</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.090572946936514</v>
+        <v>-5.064654667404526</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.704835405997807</v>
+        <v>1.715202717810602</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.2334279666094805</v>
+        <v>0.259346246141468</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.881477789051848</v>
+        <v>3.897028756771041</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.736498861822349</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.236593633850476</v>
+        <v>-5.210675354318488</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.641504983968411</v>
+        <v>1.651872295781207</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.2243448748156235</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.871105786711723</v>
+        <v>3.886656754430916</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.898702918521393</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.328307642960061</v>
+        <v>-5.302389363428073</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.767023437023622</v>
+        <v>1.777390748836417</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.2243448748156235</v>
+        <v>0.250263154347611</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.033309843410768</v>
+        <v>4.04886081112996</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.893549556485207</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.35995930202003</v>
+        <v>-5.334041022488043</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.749209411363448</v>
+        <v>1.759576723176243</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2191764175711833</v>
+        <v>0.2450946971031708</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.025055407027918</v>
+        <v>4.04060637474711</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.903778974053699</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.441894120288914</v>
+        <v>-5.415975840756926</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.726664901624386</v>
+        <v>1.737032213437181</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2092416719841032</v>
+        <v>0.2351599515160906</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.029323977244161</v>
+        <v>4.044874944963353</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.912704612509601</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.543870242537321</v>
+        <v>-5.415632791360642</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.694800091180925</v>
+        <v>1.746095071651597</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1072655497356956</v>
+        <v>0.2355030009123743</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.977063942351019</v>
+        <v>4.054006413057026</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.904857499753776</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.433863959060099</v>
+        <v>-5.305626507883421</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.73095549181599</v>
+        <v>1.782250472286661</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1304701216529708</v>
+        <v>0.2587075728296495</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.983139572745559</v>
+        <v>4.060082043451566</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.909107510475751</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.290804383319173</v>
+        <v>-5.162566932142495</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.792429332834334</v>
+        <v>1.843724313305005</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1384835482429501</v>
+        <v>0.2667209994196288</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.992197639421521</v>
+        <v>4.069140110127528</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.916368393358287</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.989357657847336</v>
+        <v>-4.861120206670657</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.920268905905605</v>
+        <v>1.971563886376277</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4399302737147873</v>
+        <v>0.5681677248914661</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.18032655758716</v>
+        <v>4.257269028293167</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.917339571110997</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.01394790208252</v>
+        <v>-4.885710450905841</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.911403985964242</v>
+        <v>1.962698966434913</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4399302737147873</v>
+        <v>0.5681677248914661</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.18129773533987</v>
+        <v>4.258240206045877</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.918182475490752</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.962909526075999</v>
+        <v>-4.834672074899321</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.932662240746605</v>
+        <v>1.983957221217277</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4399302737147873</v>
+        <v>0.5681677248914661</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.182140639719625</v>
+        <v>4.259083110425633</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.937220574364898</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.921770231209369</v>
+        <v>-4.79353278003269</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.968156057567403</v>
+        <v>2.019451038038075</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4810695685814181</v>
+        <v>0.6093070197580969</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.225862315513749</v>
+        <v>4.302804786219756</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.753404570488832</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.825135319190728</v>
+        <v>-4.69689786801405</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.822994018498794</v>
+        <v>1.874288998969465</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5777044806000581</v>
+        <v>0.7059419317767368</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.100027258848868</v>
+        <v>4.176969729554875</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.756906614562796</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.955716053721571</v>
+        <v>-4.827478602544892</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.77426376876042</v>
+        <v>1.825558749231092</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4471237460692156</v>
+        <v>0.5753611972458943</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.025180862204325</v>
+        <v>4.102123332910333</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833458</v>
       </c>
       <c r="C2035" t="n">
         <v>3.741333433638879</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.791219719530609</v>
+        <v>-4.662982268353931</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.824489121512888</v>
+        <v>1.875784101983559</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6116200802601774</v>
+        <v>0.7398575314368562</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.108305481794986</v>
+        <v>4.185247952500992</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077629</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.740521144075308</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.818589652215041</v>
+        <v>-4.690352201038363</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.812728858875545</v>
+        <v>1.864023839346216</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6116200802601774</v>
+        <v>0.7398575314368562</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.107493192231415</v>
+        <v>4.184435662937422</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.750389923200381</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.828974847104931</v>
+        <v>-4.700737395928252</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.818443560044661</v>
+        <v>1.869738540515333</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6012348853702881</v>
+        <v>0.7294723365469669</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.111130854422554</v>
+        <v>4.188073325128562</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.821226928976806</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.847563005827156</v>
+        <v>-4.719325554650477</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.881845302332196</v>
+        <v>1.933140282802868</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5826467266480628</v>
+        <v>0.7108841778247414</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.170814964965644</v>
+        <v>4.247757435671651</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.818095939795104</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.847861552523192</v>
+        <v>-4.719624101346513</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.878594894472081</v>
+        <v>1.929889874942752</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5826467266480628</v>
+        <v>0.7105856311287055</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.167683975783943</v>
+        <v>4.244447318472328</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.822626834734496</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.747038418832764</v>
+        <v>-4.618800967656085</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.923455042887643</v>
+        <v>1.974750023358315</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5951109421324167</v>
+        <v>0.7230498466130594</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.179693400013946</v>
+        <v>4.256456742702332</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.822756088213039</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.556257058080357</v>
+        <v>-4.428019606903678</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.999896840667149</v>
+        <v>2.051191821137821</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.785892302884824</v>
+        <v>0.9138312073654667</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.294291469943934</v>
+        <v>4.37105481263232</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.802592933950636</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.537740204038537</v>
+        <v>-4.409502752861858</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.987140428021474</v>
+        <v>2.038435408492145</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7988224323100322</v>
+        <v>0.926761336790675</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.281886393336655</v>
+        <v>4.358649736025041</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.837559870562694</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.512547019537219</v>
+        <v>-4.38430956836054</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.032184638434059</v>
+        <v>2.083479618904731</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8240156168113506</v>
+        <v>0.9519545212919933</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.331969240649505</v>
+        <v>4.408732583337891</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.831246438464132</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.500492892624256</v>
+        <v>-4.372255441447577</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.030692857100682</v>
+        <v>2.081987837571353</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8360697437243134</v>
+        <v>0.9640086482049561</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.33288828469872</v>
+        <v>4.409651627387106</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.833127068648268</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.507116139314614</v>
+        <v>-4.378878688137935</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.029924188608675</v>
+        <v>2.081219169079346</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.829446497033955</v>
+        <v>0.9573854015145977</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.330794966868641</v>
+        <v>4.407558309557027</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.84597809452615</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.404235549786021</v>
+        <v>-4.275998098609342</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.083927450297995</v>
+        <v>2.135222430768666</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9323270865625479</v>
+        <v>1.060265991043191</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.405374346463679</v>
+        <v>4.482137689152065</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.427677588966108</v>
+        <v>-4.299440137789429</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.094753304799554</v>
+        <v>2.146048285270226</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9323270865625479</v>
+        <v>1.060265991043191</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.425577016637273</v>
+        <v>4.502340359325659</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.866180764699744</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.44575009725772</v>
+        <v>-4.317512646081041</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.087524301482909</v>
+        <v>2.138819281953581</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9323270865625479</v>
+        <v>1.060265991043191</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.425577016637273</v>
+        <v>4.502340359325659</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.826432678293211</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.676923891134352</v>
+        <v>-4.548686439957673</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.955306697525723</v>
+        <v>2.006601677996394</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9323270865625479</v>
+        <v>1.060265991043191</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.38582893023074</v>
+        <v>4.462592272919125</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.833455297290151</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.645637870593896</v>
+        <v>-4.517400419417218</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.974843724738845</v>
+        <v>2.026138705209517</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9636131071030033</v>
+        <v>1.091552011583646</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.411623161551953</v>
+        <v>4.488386504240339</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.932626296863055</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.492612478480612</v>
+        <v>-4.364375027303933</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.135224881157063</v>
+        <v>2.186519861627734</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.116638499216287</v>
+        <v>1.24457740369693</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.602609396392828</v>
+        <v>4.679372739081213</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.120092521771348</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.520919792353882</v>
+        <v>-4.392682341177204</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.311368180516047</v>
+        <v>2.362663160986719</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.116638499216287</v>
+        <v>1.24457740369693</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.790075621301121</v>
+        <v>4.866838963989506</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>4.08949547312543</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.687513017467404</v>
+        <v>-4.559275566290726</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.214133841824721</v>
+        <v>2.265428822295392</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.950045274102765</v>
+        <v>1.077984178583408</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.659522637587089</v>
+        <v>4.736285980275475</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>4.093171875787148</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.514448638085105</v>
+        <v>-4.386211186908426</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.287035996239358</v>
+        <v>2.33833097671003</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.950045274102765</v>
+        <v>1.077984178583408</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.663199040248807</v>
+        <v>4.739962382937192</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>4.090789930910643</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.485202657629408</v>
+        <v>-4.356965206452729</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.296352443545132</v>
+        <v>2.347647424015804</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.950045274102765</v>
+        <v>1.077984178583408</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.660817095372302</v>
+        <v>4.737580438060688</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>4.088083170068278</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.592128205507259</v>
+        <v>-4.46389075433058</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.250875463551627</v>
+        <v>2.302170444022298</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8431197262249136</v>
+        <v>0.9710586307055563</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.593955005803227</v>
+        <v>4.670718348491611</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>4.089511972211512</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.737146764014508</v>
+        <v>-4.608909312837829</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.194296842291962</v>
+        <v>2.245591822762633</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.6981011677176651</v>
+        <v>0.8260400721983078</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.508372672842111</v>
+        <v>4.585136015530497</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.189443211469265</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.855488529799225</v>
+        <v>-4.727251078622547</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.246891375235828</v>
+        <v>2.298186355706499</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7087872062805551</v>
+        <v>0.8367261107611978</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.614715535237599</v>
+        <v>4.691478877925984</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.187228908595204</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.906898952119933</v>
+        <v>-4.778661500943254</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.224112903433483</v>
+        <v>2.275407883904155</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7087872062805551</v>
+        <v>0.8367261107611978</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.612501232363537</v>
+        <v>4.689264575051922</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720068</v>
+        <v>3.70477813472007</v>
       </c>
       <c r="C2060" t="n">
         <v>4.187132036669493</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.986318403327685</v>
+        <v>-4.858080952151006</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.192248251024672</v>
+        <v>2.243543231495344</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7087872062805551</v>
+        <v>0.8367261107611978</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.612404360437827</v>
+        <v>4.689167703126213</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.739867861186503</v>
+        <v>3.866907019738589</v>
       </c>
       <c r="C2061" t="n">
         <v>4.187125930227537</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.936158757282457</v>
+        <v>-5.001714151670193</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.212306003000807</v>
+        <v>2.186083845245713</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7087872062805551</v>
+        <v>0.8367261107611978</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.61239825399587</v>
+        <v>4.689161596684256</v>
       </c>
     </row>
   </sheetData>
